--- a/InputData/ctrl-settings/BAEPAbCiPC/Bool Are Energy Prices Affected by Chng in Production Costs.xlsx
+++ b/InputData/ctrl-settings/BAEPAbCiPC/Bool Are Energy Prices Affected by Chng in Production Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\BAEPAbCiPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\CA\ctrl-settings\BAEPAbCiPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEA0A00-D6A6-4D26-8247-961C9C80FF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B2C264A-4EE8-44B1-894C-9B8B35EB40D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9795" yWindow="825" windowWidth="18765" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Source:</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>We use it only for the fuel types that are energy carriers within the EPS.</t>
+  </si>
+  <si>
+    <t>California</t>
   </si>
 </sst>
 </file>
@@ -180,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -188,6 +191,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,15 +472,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,22 +494,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
